--- a/Team-Data/2007-08/2-19-2007-08.xlsx
+++ b/Team-Data/2007-08/2-19-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
         <v>22</v>
       </c>
       <c r="F2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G2" t="n">
-        <v>0.431</v>
+        <v>0.44</v>
       </c>
       <c r="H2" t="n">
         <v>48.6</v>
@@ -682,16 +749,16 @@
         <v>79.3</v>
       </c>
       <c r="K2" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L2" t="n">
         <v>3.7</v>
       </c>
       <c r="M2" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="N2" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O2" t="n">
         <v>21.1</v>
@@ -712,22 +779,22 @@
         <v>42.1</v>
       </c>
       <c r="U2" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V2" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W2" t="n">
         <v>7.8</v>
       </c>
       <c r="X2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Y2" t="n">
         <v>5.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AA2" t="n">
         <v>21.9</v>
@@ -736,25 +803,25 @@
         <v>94.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2.1</v>
+        <v>-1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>20</v>
       </c>
       <c r="AF2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG2" t="n">
         <v>18</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>19</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
       </c>
       <c r="AI2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ2" t="n">
         <v>21</v>
@@ -766,7 +833,7 @@
         <v>29</v>
       </c>
       <c r="AM2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AN2" t="n">
         <v>29</v>
@@ -784,16 +851,16 @@
         <v>5</v>
       </c>
       <c r="AS2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -811,10 +878,10 @@
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -843,37 +910,37 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="n">
         <v>41</v>
       </c>
       <c r="F3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.804</v>
+        <v>0.82</v>
       </c>
       <c r="H3" t="n">
         <v>48.2</v>
       </c>
       <c r="I3" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J3" t="n">
-        <v>75.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.472</v>
+        <v>0.473</v>
       </c>
       <c r="L3" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M3" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="N3" t="n">
-        <v>0.379</v>
+        <v>0.381</v>
       </c>
       <c r="O3" t="n">
         <v>21.1</v>
@@ -882,16 +949,16 @@
         <v>27.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.769</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S3" t="n">
         <v>31.4</v>
       </c>
       <c r="T3" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="U3" t="n">
         <v>21.8</v>
@@ -906,22 +973,22 @@
         <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.2</v>
+        <v>99.8</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,10 +1000,10 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -945,16 +1012,16 @@
         <v>4</v>
       </c>
       <c r="AL3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN3" t="n">
         <v>5</v>
       </c>
       <c r="AO3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP3" t="n">
         <v>7</v>
@@ -963,10 +1030,10 @@
         <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT3" t="n">
         <v>20</v>
@@ -975,22 +1042,22 @@
         <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AW3" t="n">
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB3" t="n">
         <v>11</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -1025,28 +1092,28 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E4" t="n">
         <v>19</v>
       </c>
       <c r="F4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G4" t="n">
-        <v>0.352</v>
+        <v>0.358</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.5</v>
+        <v>35.8</v>
       </c>
       <c r="J4" t="n">
         <v>79.7</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.449</v>
       </c>
       <c r="L4" t="n">
         <v>6.1</v>
@@ -1055,7 +1122,7 @@
         <v>17.2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O4" t="n">
         <v>17.8</v>
@@ -1073,34 +1140,34 @@
         <v>29.2</v>
       </c>
       <c r="T4" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U4" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V4" t="n">
         <v>15.1</v>
       </c>
       <c r="W4" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X4" t="n">
         <v>5</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="AA4" t="n">
         <v>21.1</v>
       </c>
       <c r="AB4" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC4" t="n">
-        <v>-5.5</v>
+        <v>-5.2</v>
       </c>
       <c r="AD4" t="n">
         <v>2</v>
@@ -1109,28 +1176,28 @@
         <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AG4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AJ4" t="n">
         <v>18</v>
       </c>
       <c r="AK4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>17</v>
       </c>
       <c r="AM4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN4" t="n">
         <v>15</v>
@@ -1142,7 +1209,7 @@
         <v>14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR4" t="n">
         <v>18</v>
@@ -1154,10 +1221,10 @@
         <v>24</v>
       </c>
       <c r="AU4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
         <v>17</v>
@@ -1175,10 +1242,10 @@
         <v>17</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BC4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1352,22 @@
         <v>-2.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
         <v>21</v>
       </c>
       <c r="AF5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG5" t="n">
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
         <v>6</v>
@@ -1318,7 +1385,7 @@
         <v>17</v>
       </c>
       <c r="AO5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>19</v>
@@ -1336,13 +1403,13 @@
         <v>7</v>
       </c>
       <c r="AU5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AW5" t="n">
         <v>14</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>13</v>
       </c>
       <c r="AX5" t="n">
         <v>14</v>
@@ -1357,7 +1424,7 @@
         <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -1389,31 +1456,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
-        <v>0.547</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.7</v>
       </c>
       <c r="I6" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J6" t="n">
         <v>82.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.438</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M6" t="n">
         <v>18.8</v>
@@ -1434,10 +1501,10 @@
         <v>13</v>
       </c>
       <c r="S6" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
-        <v>44.2</v>
+        <v>44.1</v>
       </c>
       <c r="U6" t="n">
         <v>19.4</v>
@@ -1458,37 +1525,37 @@
         <v>21.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB6" t="n">
-        <v>97</v>
+        <v>97.3</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.4</v>
+        <v>-1.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
       </c>
       <c r="AF6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AG6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH6" t="n">
         <v>2</v>
       </c>
       <c r="AI6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ6" t="n">
         <v>9</v>
       </c>
       <c r="AK6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>11</v>
@@ -1509,7 +1576,7 @@
         <v>27</v>
       </c>
       <c r="AR6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS6" t="n">
         <v>12</v>
@@ -1527,7 +1594,7 @@
         <v>11</v>
       </c>
       <c r="AX6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY6" t="n">
         <v>15</v>
@@ -1536,10 +1603,10 @@
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BB6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -1649,10 +1716,10 @@
         <v>3.9</v>
       </c>
       <c r="AD7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE7" t="n">
         <v>5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>6</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
@@ -1661,7 +1728,7 @@
         <v>7</v>
       </c>
       <c r="AH7" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AI7" t="n">
         <v>15</v>
@@ -1673,19 +1740,19 @@
         <v>6</v>
       </c>
       <c r="AL7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AM7" t="n">
         <v>19</v>
       </c>
       <c r="AN7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO7" t="n">
         <v>8</v>
       </c>
       <c r="AP7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1706,7 +1773,7 @@
         <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX7" t="n">
         <v>13</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -1753,16 +1820,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F8" t="n">
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.623</v>
+        <v>0.615</v>
       </c>
       <c r="H8" t="n">
         <v>48.5</v>
@@ -1771,10 +1838,10 @@
         <v>38.7</v>
       </c>
       <c r="J8" t="n">
-        <v>85.2</v>
+        <v>85.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L8" t="n">
         <v>6.3</v>
@@ -1783,28 +1850,28 @@
         <v>18.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0.34</v>
+        <v>0.338</v>
       </c>
       <c r="O8" t="n">
-        <v>23.2</v>
+        <v>23</v>
       </c>
       <c r="P8" t="n">
-        <v>30.6</v>
+        <v>30.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.759</v>
+        <v>0.761</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S8" t="n">
-        <v>32.8</v>
+        <v>32.7</v>
       </c>
       <c r="T8" t="n">
         <v>44.8</v>
       </c>
       <c r="U8" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
         <v>15.5</v>
@@ -1813,25 +1880,25 @@
         <v>9.4</v>
       </c>
       <c r="X8" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="Y8" t="n">
         <v>5.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.1</v>
+        <v>24</v>
       </c>
       <c r="AB8" t="n">
-        <v>107</v>
+        <v>106.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1843,7 +1910,7 @@
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
@@ -1852,7 +1919,7 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AL8" t="n">
         <v>16</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1900,7 +1967,7 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
         <v>4</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -1935,37 +2002,37 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
         <v>39</v>
       </c>
       <c r="F9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" t="n">
-        <v>0.736</v>
+        <v>0.75</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="J9" t="n">
         <v>79.5</v>
       </c>
       <c r="K9" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L9" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
         <v>16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.375</v>
+        <v>0.379</v>
       </c>
       <c r="O9" t="n">
         <v>18.6</v>
@@ -1977,16 +2044,16 @@
         <v>0.755</v>
       </c>
       <c r="R9" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S9" t="n">
         <v>29.4</v>
       </c>
       <c r="T9" t="n">
-        <v>41</v>
+        <v>40.9</v>
       </c>
       <c r="U9" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="V9" t="n">
         <v>11.6</v>
@@ -1998,7 +2065,7 @@
         <v>5.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z9" t="n">
         <v>20.6</v>
@@ -2007,13 +2074,13 @@
         <v>20.3</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.40000000000001</v>
+        <v>97.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,7 +2095,7 @@
         <v>26</v>
       </c>
       <c r="AI9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
@@ -2049,13 +2116,13 @@
         <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ9" t="n">
         <v>15</v>
       </c>
       <c r="AR9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>25</v>
@@ -2073,7 +2140,7 @@
         <v>15</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
         <v>1</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" t="n">
         <v>32</v>
       </c>
       <c r="F10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>0.604</v>
+        <v>0.615</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
@@ -2135,10 +2202,10 @@
         <v>40.5</v>
       </c>
       <c r="J10" t="n">
-        <v>88.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L10" t="n">
         <v>9.699999999999999</v>
@@ -2147,28 +2214,28 @@
         <v>27.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O10" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P10" t="n">
-        <v>25.6</v>
+        <v>25.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.748</v>
+        <v>0.749</v>
       </c>
       <c r="R10" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S10" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42</v>
+        <v>42.2</v>
       </c>
       <c r="U10" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V10" t="n">
         <v>13.5</v>
@@ -2183,7 +2250,7 @@
         <v>4.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="AA10" t="n">
         <v>22.2</v>
@@ -2192,19 +2259,19 @@
         <v>109.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AG10" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AH10" t="n">
         <v>17</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2228,10 +2295,10 @@
         <v>16</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ10" t="n">
         <v>18</v>
@@ -2240,10 +2307,10 @@
         <v>9</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AU10" t="n">
         <v>7</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>0.623</v>
+        <v>0.615</v>
       </c>
       <c r="H11" t="n">
         <v>48.2</v>
       </c>
       <c r="I11" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J11" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L11" t="n">
         <v>6.7</v>
@@ -2332,19 +2399,19 @@
         <v>0.338</v>
       </c>
       <c r="O11" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.729</v>
+        <v>0.73</v>
       </c>
       <c r="R11" t="n">
-        <v>12.2</v>
+        <v>12.3</v>
       </c>
       <c r="S11" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T11" t="n">
         <v>44.2</v>
@@ -2359,10 +2426,10 @@
         <v>7.5</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z11" t="n">
         <v>19.6</v>
@@ -2374,10 +2441,10 @@
         <v>95.7</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>10</v>
@@ -2398,10 +2465,10 @@
         <v>13</v>
       </c>
       <c r="AK11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM11" t="n">
         <v>9</v>
@@ -2410,7 +2477,7 @@
         <v>22</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AP11" t="n">
         <v>24</v>
@@ -2425,7 +2492,7 @@
         <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU11" t="n">
         <v>11</v>
@@ -2434,7 +2501,7 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>4</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2571,10 +2638,10 @@
         <v>22</v>
       </c>
       <c r="AH12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ12" t="n">
         <v>2</v>
@@ -2598,7 +2665,7 @@
         <v>21</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-4.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2762,16 +2829,16 @@
         <v>24</v>
       </c>
       <c r="AK13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM13" t="n">
         <v>27</v>
       </c>
       <c r="AN13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO13" t="n">
         <v>9</v>
@@ -2792,7 +2859,7 @@
         <v>26</v>
       </c>
       <c r="AU13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -2845,70 +2912,70 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" t="n">
         <v>17</v>
       </c>
       <c r="G14" t="n">
-        <v>0.679</v>
+        <v>0.673</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>39.2</v>
+        <v>39</v>
       </c>
       <c r="J14" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
         <v>7.4</v>
       </c>
       <c r="M14" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O14" t="n">
         <v>21.6</v>
       </c>
       <c r="P14" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.759</v>
+        <v>0.756</v>
       </c>
       <c r="R14" t="n">
         <v>10.8</v>
       </c>
       <c r="S14" t="n">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="T14" t="n">
         <v>44.2</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W14" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z14" t="n">
         <v>20.9</v>
@@ -2917,16 +2984,16 @@
         <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.4</v>
+        <v>107.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="AD14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE14" t="n">
         <v>5</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>4</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
@@ -2947,19 +3014,19 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AO14" t="n">
         <v>3</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
         <v>14</v>
@@ -2968,7 +3035,7 @@
         <v>20</v>
       </c>
       <c r="AS14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT14" t="n">
         <v>3</v>
@@ -2977,16 +3044,16 @@
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ14" t="n">
         <v>12</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -3027,49 +3094,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E15" t="n">
         <v>14</v>
       </c>
       <c r="F15" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.264</v>
+        <v>0.269</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J15" t="n">
-        <v>81</v>
+        <v>80.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L15" t="n">
         <v>7.9</v>
       </c>
       <c r="M15" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O15" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P15" t="n">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0.737</v>
       </c>
       <c r="R15" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="S15" t="n">
         <v>31.7</v>
@@ -3078,16 +3145,16 @@
         <v>41.7</v>
       </c>
       <c r="U15" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="V15" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W15" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="X15" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6</v>
@@ -3105,43 +3172,43 @@
         <v>-4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AI15" t="n">
         <v>10</v>
       </c>
       <c r="AJ15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK15" t="n">
         <v>9</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
       </c>
       <c r="AN15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ15" t="n">
         <v>21</v>
@@ -3150,7 +3217,7 @@
         <v>23</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT15" t="n">
         <v>18</v>
@@ -3162,10 +3229,10 @@
         <v>29</v>
       </c>
       <c r="AW15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3177,7 +3244,7 @@
         <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
         <v>23</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-7.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI16" t="n">
         <v>26</v>
@@ -3308,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL16" t="n">
         <v>25</v>
@@ -3317,7 +3384,7 @@
         <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO16" t="n">
         <v>19</v>
@@ -3356,13 +3423,13 @@
         <v>11</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>-6.5</v>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>23</v>
@@ -3481,7 +3548,7 @@
         <v>23</v>
       </c>
       <c r="AH17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3490,7 +3557,7 @@
         <v>16</v>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
@@ -3499,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO17" t="n">
         <v>26</v>
@@ -3511,7 +3578,7 @@
         <v>20</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS17" t="n">
         <v>30</v>
@@ -3538,7 +3605,7 @@
         <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB17" t="n">
         <v>25</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -3573,28 +3640,28 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F18" t="n">
         <v>41</v>
       </c>
       <c r="G18" t="n">
-        <v>0.212</v>
+        <v>0.196</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
       </c>
       <c r="I18" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J18" t="n">
         <v>83.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L18" t="n">
         <v>5.4</v>
@@ -3606,13 +3673,13 @@
         <v>0.331</v>
       </c>
       <c r="O18" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.724</v>
+        <v>0.725</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
@@ -3624,19 +3691,19 @@
         <v>42.3</v>
       </c>
       <c r="U18" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="V18" t="n">
         <v>15.4</v>
       </c>
       <c r="W18" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X18" t="n">
         <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z18" t="n">
         <v>23.6</v>
@@ -3645,13 +3712,13 @@
         <v>17.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>93.5</v>
+        <v>93.3</v>
       </c>
       <c r="AC18" t="n">
-        <v>-7.3</v>
+        <v>-7.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE18" t="n">
         <v>29</v>
@@ -3666,16 +3733,16 @@
         <v>30</v>
       </c>
       <c r="AI18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AM18" t="n">
         <v>22</v>
@@ -3690,25 +3757,25 @@
         <v>28</v>
       </c>
       <c r="AQ18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV18" t="n">
         <v>23</v>
       </c>
       <c r="AW18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
@@ -3726,7 +3793,7 @@
         <v>29</v>
       </c>
       <c r="BC18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -3833,19 +3900,19 @@
         <v>-5.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF19" t="n">
         <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>30</v>
@@ -3872,7 +3939,7 @@
         <v>5</v>
       </c>
       <c r="AQ19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
         <v>14</v>
@@ -3881,7 +3948,7 @@
         <v>15</v>
       </c>
       <c r="AT19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU19" t="n">
         <v>3</v>
@@ -3908,7 +3975,7 @@
         <v>28</v>
       </c>
       <c r="BC19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>5.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE20" t="n">
         <v>4</v>
@@ -4027,7 +4094,7 @@
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
@@ -4066,7 +4133,7 @@
         <v>8</v>
       </c>
       <c r="AU20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -4119,64 +4186,64 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="n">
         <v>37</v>
       </c>
       <c r="G21" t="n">
-        <v>0.302</v>
+        <v>0.288</v>
       </c>
       <c r="H21" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
         <v>35</v>
       </c>
       <c r="J21" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L21" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="M21" t="n">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="N21" t="n">
-        <v>0.335</v>
+        <v>0.334</v>
       </c>
       <c r="O21" t="n">
-        <v>19.3</v>
+        <v>19</v>
       </c>
       <c r="P21" t="n">
-        <v>26.6</v>
+        <v>26.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.725</v>
+        <v>0.723</v>
       </c>
       <c r="R21" t="n">
         <v>12.3</v>
       </c>
       <c r="S21" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
         <v>41.9</v>
       </c>
       <c r="U21" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="V21" t="n">
         <v>15.5</v>
       </c>
       <c r="W21" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
@@ -4185,19 +4252,19 @@
         <v>5.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AA21" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.09999999999999</v>
+        <v>94.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.6</v>
+        <v>-5.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,40 +4276,40 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
         <v>19</v>
       </c>
       <c r="AK21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN21" t="n">
         <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
         <v>9</v>
       </c>
       <c r="AQ21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS21" t="n">
         <v>24</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>23</v>
       </c>
       <c r="AT21" t="n">
         <v>17</v>
@@ -4254,7 +4321,7 @@
         <v>24</v>
       </c>
       <c r="AW21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4266,10 +4333,10 @@
         <v>19</v>
       </c>
       <c r="BA21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB21" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
         <v>26</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -4301,16 +4368,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F22" t="n">
         <v>21</v>
       </c>
       <c r="G22" t="n">
-        <v>0.618</v>
+        <v>0.611</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
@@ -4319,37 +4386,37 @@
         <v>36.8</v>
       </c>
       <c r="J22" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K22" t="n">
         <v>0.469</v>
       </c>
       <c r="L22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="M22" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0.374</v>
+        <v>0.369</v>
       </c>
       <c r="O22" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="P22" t="n">
-        <v>29.1</v>
+        <v>29.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.726</v>
+        <v>0.725</v>
       </c>
       <c r="R22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S22" t="n">
         <v>32.6</v>
       </c>
       <c r="T22" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U22" t="n">
         <v>20.1</v>
@@ -4364,19 +4431,19 @@
         <v>4.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="Z22" t="n">
         <v>21.3</v>
       </c>
       <c r="AA22" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AB22" t="n">
         <v>104</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="AD22" t="n">
         <v>1</v>
@@ -4385,10 +4452,10 @@
         <v>9</v>
       </c>
       <c r="AF22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
@@ -4409,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4421,13 +4488,13 @@
         <v>23</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS22" t="n">
         <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU22" t="n">
         <v>23</v>
@@ -4442,13 +4509,13 @@
         <v>22</v>
       </c>
       <c r="AY22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ22" t="n">
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB22" t="n">
         <v>6</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" t="n">
         <v>23</v>
       </c>
       <c r="F23" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G23" t="n">
-        <v>0.426</v>
+        <v>0.434</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,7 +4568,7 @@
         <v>36.4</v>
       </c>
       <c r="J23" t="n">
-        <v>80.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K23" t="n">
         <v>0.454</v>
@@ -4510,19 +4577,19 @@
         <v>3.6</v>
       </c>
       <c r="M23" t="n">
-        <v>11.4</v>
+        <v>11.5</v>
       </c>
       <c r="N23" t="n">
-        <v>0.313</v>
+        <v>0.315</v>
       </c>
       <c r="O23" t="n">
-        <v>17.9</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.701</v>
+        <v>0.704</v>
       </c>
       <c r="R23" t="n">
         <v>13</v>
@@ -4534,16 +4601,16 @@
         <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V23" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W23" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y23" t="n">
         <v>4.8</v>
@@ -4552,25 +4619,25 @@
         <v>20.2</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC23" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
       <c r="AD23" t="n">
         <v>2</v>
       </c>
       <c r="AE23" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG23" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH23" t="n">
         <v>25</v>
@@ -4582,13 +4649,13 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
       </c>
       <c r="AM23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AN23" t="n">
         <v>30</v>
@@ -4597,34 +4664,34 @@
         <v>20</v>
       </c>
       <c r="AP23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS23" t="n">
         <v>29</v>
       </c>
       <c r="AT23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU23" t="n">
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW23" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY23" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>5.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4755,7 +4822,7 @@
         <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI24" t="n">
         <v>1</v>
@@ -4812,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E25" t="n">
         <v>28</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>0.528</v>
+        <v>0.538</v>
       </c>
       <c r="H25" t="n">
         <v>48.8</v>
       </c>
       <c r="I25" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J25" t="n">
-        <v>78.90000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="K25" t="n">
         <v>0.453</v>
@@ -4874,58 +4941,58 @@
         <v>6.4</v>
       </c>
       <c r="M25" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O25" t="n">
-        <v>17.4</v>
+        <v>17.6</v>
       </c>
       <c r="P25" t="n">
-        <v>22.9</v>
+        <v>23.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.76</v>
+        <v>0.761</v>
       </c>
       <c r="R25" t="n">
         <v>10.5</v>
       </c>
       <c r="S25" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T25" t="n">
         <v>40.2</v>
       </c>
       <c r="U25" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="V25" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W25" t="n">
         <v>5.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB25" t="n">
         <v>95.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-0.4</v>
+        <v>-0.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4958,7 +5025,7 @@
         <v>6</v>
       </c>
       <c r="AO25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP25" t="n">
         <v>22</v>
@@ -4970,13 +5037,13 @@
         <v>21</v>
       </c>
       <c r="AS25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV25" t="n">
         <v>6</v>
@@ -4985,7 +5052,7 @@
         <v>30</v>
       </c>
       <c r="AX25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AY25" t="n">
         <v>3</v>
@@ -4997,7 +5064,7 @@
         <v>19</v>
       </c>
       <c r="BB25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC25" t="n">
         <v>15</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -5029,22 +5096,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F26" t="n">
         <v>28</v>
       </c>
       <c r="G26" t="n">
-        <v>0.462</v>
+        <v>0.451</v>
       </c>
       <c r="H26" t="n">
         <v>48.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
         <v>79.2</v>
@@ -5053,22 +5120,22 @@
         <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M26" t="n">
         <v>17.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="O26" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="P26" t="n">
-        <v>27.5</v>
+        <v>27.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.792</v>
+        <v>0.791</v>
       </c>
       <c r="R26" t="n">
         <v>10.3</v>
@@ -5077,13 +5144,13 @@
         <v>29.8</v>
       </c>
       <c r="T26" t="n">
-        <v>40.1</v>
+        <v>40</v>
       </c>
       <c r="U26" t="n">
         <v>18.8</v>
       </c>
       <c r="V26" t="n">
-        <v>16.3</v>
+        <v>16.4</v>
       </c>
       <c r="W26" t="n">
         <v>8.1</v>
@@ -5092,28 +5159,28 @@
         <v>3.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z26" t="n">
         <v>22.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AB26" t="n">
-        <v>100.3</v>
+        <v>100.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.8</v>
+        <v>-2.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE26" t="n">
         <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG26" t="n">
         <v>17</v>
@@ -5122,7 +5189,7 @@
         <v>22</v>
       </c>
       <c r="AI26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ26" t="n">
         <v>22</v>
@@ -5134,10 +5201,10 @@
         <v>15</v>
       </c>
       <c r="AM26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>2</v>
@@ -5152,7 +5219,7 @@
         <v>22</v>
       </c>
       <c r="AS26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
         <v>29</v>
@@ -5167,22 +5234,22 @@
         <v>7</v>
       </c>
       <c r="AX26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AY26" t="n">
         <v>24</v>
       </c>
       <c r="AZ26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F27" t="n">
         <v>17</v>
       </c>
       <c r="G27" t="n">
-        <v>0.673</v>
+        <v>0.667</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>35.9</v>
+        <v>36</v>
       </c>
       <c r="J27" t="n">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K27" t="n">
         <v>0.458</v>
@@ -5238,10 +5305,10 @@
         <v>7.9</v>
       </c>
       <c r="M27" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O27" t="n">
         <v>16.5</v>
@@ -5253,46 +5320,46 @@
         <v>0.754</v>
       </c>
       <c r="R27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="S27" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T27" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U27" t="n">
         <v>21.6</v>
       </c>
       <c r="V27" t="n">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA27" t="n">
         <v>19.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF27" t="n">
         <v>5</v>
@@ -5310,10 +5377,10 @@
         <v>27</v>
       </c>
       <c r="AK27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM27" t="n">
         <v>6</v>
@@ -5322,19 +5389,19 @@
         <v>4</v>
       </c>
       <c r="AO27" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AP27" t="n">
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR27" t="n">
         <v>24</v>
       </c>
       <c r="AS27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT27" t="n">
         <v>19</v>
@@ -5349,7 +5416,7 @@
         <v>23</v>
       </c>
       <c r="AX27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
         <v>12</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -5393,37 +5460,37 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" t="n">
         <v>38</v>
       </c>
       <c r="G28" t="n">
-        <v>0.269</v>
+        <v>0.255</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
       </c>
       <c r="I28" t="n">
-        <v>37.6</v>
+        <v>37.5</v>
       </c>
       <c r="J28" t="n">
-        <v>85.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.441</v>
+        <v>0.44</v>
       </c>
       <c r="L28" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.338</v>
+        <v>0.333</v>
       </c>
       <c r="O28" t="n">
         <v>17.5</v>
@@ -5432,22 +5499,22 @@
         <v>22.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.767</v>
+        <v>0.769</v>
       </c>
       <c r="R28" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S28" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T28" t="n">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="U28" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="V28" t="n">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="W28" t="n">
         <v>6.5</v>
@@ -5465,28 +5532,28 @@
         <v>20</v>
       </c>
       <c r="AB28" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>-7</v>
+        <v>-7.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AE28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF28" t="n">
         <v>27</v>
       </c>
       <c r="AG28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AH28" t="n">
         <v>16</v>
       </c>
       <c r="AI28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ28" t="n">
         <v>3</v>
@@ -5495,28 +5562,28 @@
         <v>23</v>
       </c>
       <c r="AL28" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM28" t="n">
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AO28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AP28" t="n">
         <v>23</v>
       </c>
       <c r="AQ28" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR28" t="n">
         <v>11</v>
       </c>
-      <c r="AR28" t="n">
-        <v>12</v>
-      </c>
       <c r="AS28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT28" t="n">
         <v>1</v>
@@ -5531,7 +5598,7 @@
         <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY28" t="n">
         <v>23</v>
@@ -5540,10 +5607,10 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB28" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC28" t="n">
         <v>28</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>3.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AE29" t="n">
         <v>14</v>
@@ -5662,10 +5729,10 @@
         <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AH29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>9</v>
@@ -5701,7 +5768,7 @@
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AU29" t="n">
         <v>6</v>
@@ -5713,13 +5780,13 @@
         <v>20</v>
       </c>
       <c r="AX29" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ29" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -5757,88 +5824,88 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
         <v>19</v>
       </c>
       <c r="G30" t="n">
-        <v>0.648</v>
+        <v>0.642</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
       </c>
       <c r="I30" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.492</v>
+        <v>0.491</v>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M30" t="n">
         <v>12.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0.369</v>
+        <v>0.366</v>
       </c>
       <c r="O30" t="n">
         <v>21.5</v>
       </c>
       <c r="P30" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.755</v>
+        <v>0.752</v>
       </c>
       <c r="R30" t="n">
         <v>11.5</v>
       </c>
       <c r="S30" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>40.9</v>
+        <v>40.8</v>
       </c>
       <c r="U30" t="n">
-        <v>26.3</v>
+        <v>26.2</v>
       </c>
       <c r="V30" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="W30" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="X30" t="n">
         <v>4.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>24.6</v>
+        <v>24.7</v>
       </c>
       <c r="AA30" t="n">
         <v>23.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>105.6</v>
+        <v>105.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="AD30" t="n">
         <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AF30" t="n">
         <v>8</v>
@@ -5847,13 +5914,13 @@
         <v>8</v>
       </c>
       <c r="AH30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AI30" t="n">
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5865,19 +5932,19 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO30" t="n">
         <v>4</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS30" t="n">
         <v>26</v>
@@ -5889,13 +5956,13 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E31" t="n">
         <v>25</v>
       </c>
       <c r="F31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G31" t="n">
-        <v>0.472</v>
+        <v>0.481</v>
       </c>
       <c r="H31" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I31" t="n">
         <v>36.3</v>
       </c>
       <c r="J31" t="n">
-        <v>82</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.442</v>
+        <v>0.443</v>
       </c>
       <c r="L31" t="n">
         <v>6.6</v>
@@ -5990,10 +6057,10 @@
         <v>42.4</v>
       </c>
       <c r="U31" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="V31" t="n">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="W31" t="n">
         <v>7.7</v>
@@ -6005,7 +6072,7 @@
         <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AA31" t="n">
         <v>20.1</v>
@@ -6014,10 +6081,10 @@
         <v>98.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>16</v>
@@ -6029,7 +6096,7 @@
         <v>16</v>
       </c>
       <c r="AH31" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI31" t="n">
         <v>16</v>
@@ -6044,7 +6111,7 @@
         <v>13</v>
       </c>
       <c r="AM31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN31" t="n">
         <v>18</v>
@@ -6068,7 +6135,7 @@
         <v>10</v>
       </c>
       <c r="AU31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
@@ -6080,10 +6147,10 @@
         <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-19-2007-08</t>
+          <t>2008-02-19</t>
         </is>
       </c>
     </row>
